--- a/VT_Model_SUP_V01.xlsx
+++ b/VT_Model_SUP_V01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasiu\Desktop\Praca Magisterska\Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1088F750-5FF2-47FC-B99E-3BC3488ACE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE06E340-7FCD-4606-A7E3-7FC89038E0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4015,16 +4015,16 @@
       <c r="J9" s="5"/>
     </row>
     <row r="10" spans="1:20">
-      <c r="B10" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="34">
-        <f>10*3.6/1000</f>
-        <v>3.5999999999999997E-2</v>
+      <c r="B10" t="str">
+        <f>SEC_Processes!D10</f>
+        <v>MIN_HARD_COAL</v>
+      </c>
+      <c r="D10" t="str">
+        <f>SEC_Comm!C11</f>
+        <v>HARD_COAL</v>
+      </c>
+      <c r="E10">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="29"/>
@@ -4033,32 +4033,32 @@
       <c r="J10" s="5"/>
     </row>
     <row r="11" spans="1:20">
-      <c r="B11" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="35">
-        <f>50*3.6/1000</f>
-        <v>0.18</v>
+      <c r="B11" t="str">
+        <f>SEC_Processes!D11</f>
+        <v>MIN_LIGNITE</v>
+      </c>
+      <c r="D11" t="str">
+        <f>SEC_Comm!C12</f>
+        <v>LIGNITE</v>
+      </c>
+      <c r="E11">
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:20">
-      <c r="B12" t="str">
-        <f>SEC_Processes!D10</f>
-        <v>MIN_HARD_COAL</v>
-      </c>
-      <c r="D12" t="str">
-        <f>SEC_Comm!C11</f>
-        <v>HARD_COAL</v>
-      </c>
-      <c r="E12">
-        <v>1.4999999999999999E-2</v>
+      <c r="B12" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="34">
+        <f>10*3.6/1000</f>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="F12" s="5"/>
       <c r="H12" s="14"/>
@@ -4066,16 +4066,16 @@
       <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:20">
-      <c r="B13" t="str">
-        <f>SEC_Processes!D11</f>
-        <v>MIN_LIGNITE</v>
-      </c>
-      <c r="D13" t="str">
-        <f>SEC_Comm!C12</f>
-        <v>LIGNITE</v>
-      </c>
-      <c r="E13">
-        <v>7.0000000000000001E-3</v>
+      <c r="B13" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="35">
+        <f>50*3.6/1000</f>
+        <v>0.18</v>
       </c>
       <c r="F13" s="5"/>
       <c r="H13" s="14"/>
@@ -4159,6 +4159,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="853a583b-5a39-49db-b57b-0c8a2ee0f312" xsi:nil="true"/>
@@ -4167,15 +4176,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4380,20 +4380,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BEC55BD-C1AB-47C6-923C-1E0B74C138B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2354E624-82C6-4C58-B5AA-5F4B4FEE1585}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="853a583b-5a39-49db-b57b-0c8a2ee0f312"/>
     <ds:schemaRef ds:uri="45d80b71-d53a-4925-9636-d69011c62a0b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BEC55BD-C1AB-47C6-923C-1E0B74C138B9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
